--- a/branches/master/ValueSet-mii-vs-icu-code-observation-bilanzen-loinc.xlsx
+++ b/branches/master/ValueSet-mii-vs-icu-code-observation-bilanzen-loinc.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.3</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/master/ValueSet-mii-vs-icu-code-observation-bilanzen-loinc.xlsx
+++ b/branches/master/ValueSet-mii-vs-icu-code-observation-bilanzen-loinc.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>Property</t>
   </si>
@@ -172,6 +172,12 @@
   </si>
   <si>
     <t>Ultrafiltrate volume removed</t>
+  </si>
+  <si>
+    <t>9057-1</t>
+  </si>
+  <si>
+    <t>Calorie intake total 24 hour</t>
   </si>
   <si>
     <t/>
@@ -444,7 +450,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -560,15 +566,23 @@
         <v>53</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
